--- a/ValidationTests.xlsx
+++ b/ValidationTests.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Mac\Home\OneDrive - DataSoar\Projects\Excel_Steps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345C970D-6AF2-45D6-A85D-949D6CA31C12}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB710A9-E12F-408B-A463-2C202774F28D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31073" yWindow="2130" windowWidth="21390" windowHeight="11917" firstSheet="1" activeTab="1" xr2:uid="{9DD4A102-5F6B-46DA-8541-48C3A19AE79F}"/>
+    <workbookView xWindow="1103" yWindow="1418" windowWidth="25312" windowHeight="15382" activeTab="2" xr2:uid="{9DD4A102-5F6B-46DA-8541-48C3A19AE79F}"/>
   </bookViews>
   <sheets>
     <sheet name="Lists" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Data" sheetId="587" r:id="rId3"/>
     <sheet name="Original Data" sheetId="585" r:id="rId4"/>
     <sheet name="ExcelSteps" sheetId="4" r:id="rId5"/>
+    <sheet name="XLStepsSettings" sheetId="588" state="veryHidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="List_Desc3">Lists!$A$2:$A$4</definedName>
@@ -30,7 +31,9 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="84">
   <si>
     <t>Sheet</t>
   </si>
@@ -169,9 +172,6 @@
     <t>Calc_4</t>
   </si>
   <si>
-    <t>=Data_Data_1*Data_Data_2</t>
-  </si>
-  <si>
     <t>Calc_5</t>
   </si>
   <si>
@@ -250,16 +250,49 @@
     <t>Part B</t>
   </si>
   <si>
-    <t>=(Data_Data_1*Data_Data_2))</t>
-  </si>
-  <si>
     <t>Excel formula error</t>
   </si>
   <si>
-    <t>Individually enable rows 13-26 as shown by entering "Data" in Columm A and refreshing the table again</t>
-  </si>
-  <si>
     <t>All Row 13-26 validation cases should produce a Refresh Error dialog box as shown and should label the Column C cell with a comment as shown</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>txtval</t>
+  </si>
+  <si>
+    <t>boolean1</t>
+  </si>
+  <si>
+    <t>boolean2</t>
+  </si>
+  <si>
+    <t>ShtNameFrm</t>
+  </si>
+  <si>
+    <t>Instructions</t>
+  </si>
+  <si>
+    <t>Original Data</t>
+  </si>
+  <si>
+    <t>cBoxAppShtName</t>
+  </si>
+  <si>
+    <t>Data_t</t>
+  </si>
+  <si>
+    <t>=@Data_Data_1*@Data_Data_2</t>
+  </si>
+  <si>
+    <t>=(@Data_Data_1*@Data_Data_2))</t>
+  </si>
+  <si>
+    <t>Missing Step name</t>
+  </si>
+  <si>
+    <t>Individually enable rows 13-27 as shown by entering "Data" in Columm A and refreshing the table again</t>
   </si>
 </sst>
 </file>
@@ -1060,43 +1093,43 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="3:3" x14ac:dyDescent="0.45">
       <c r="C32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.45">
       <c r="C33" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.45">
       <c r="C48" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1165,7 +1198,7 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
         <v>37</v>
@@ -1310,7 +1343,7 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
         <v>37</v>
@@ -1404,7 +1437,7 @@
     <col min="1" max="1" width="10" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.73046875" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.3984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.9296875" style="14" customWidth="1"/>
+    <col min="4" max="4" width="31.796875" style="14" customWidth="1"/>
     <col min="5" max="5" width="10.06640625" style="12" customWidth="1"/>
     <col min="6" max="6" width="14.265625" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="31.9296875" style="15" customWidth="1"/>
@@ -1541,7 +1574,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>22</v>
@@ -1559,13 +1592,13 @@
         <v>16</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>42</v>
@@ -1583,22 +1616,22 @@
         <v>16</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>44</v>
       </c>
       <c r="F8" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>13</v>
@@ -1636,7 +1669,7 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>17</v>
@@ -1656,7 +1689,7 @@
         <v>17</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="7"/>
@@ -1694,7 +1727,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2">
@@ -1713,7 +1746,7 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2">
@@ -1734,7 +1767,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -1753,7 +1786,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -1772,7 +1805,7 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
@@ -1790,11 +1823,11 @@
         <v>10</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -1814,7 +1847,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="2"/>
       <c r="G19" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -1823,7 +1856,7 @@
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>12</v>
@@ -1836,7 +1869,7 @@
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -1858,7 +1891,7 @@
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -1881,13 +1914,13 @@
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="7"/>
       <c r="F23" s="2"/>
       <c r="G23" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -1897,15 +1930,15 @@
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="2"/>
       <c r="G24" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -1914,16 +1947,16 @@
     <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="7"/>
       <c r="B25" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="7"/>
       <c r="F25" s="2"/>
       <c r="G25" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -1932,13 +1965,13 @@
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>22</v>
@@ -1947,21 +1980,25 @@
         <v>1</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="6"/>
+      <c r="G27" s="6" t="s">
+        <v>82</v>
+      </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
     </row>
@@ -2006,11 +2043,111 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C30" xr:uid="{9DC565B4-8D4C-4BCE-ACF2-20BB1ABACCCE}">
-      <formula1>"Col_Format, Col_Insert, Col_AddGroup, Col_Comment,Col_CondFormat, Col_Dropdown, Col_NumFormat, Col_Width, Tbl_Sort"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C30" xr:uid="{D80040AE-46D1-4EE6-8B5B-564647569365}">
+      <formula1>"Col_Format,Col_Insert,Col_AddGroup,Col_CondFormat,Col_Dropdown,Tbl_FreezeRow1,Tbl_Sort"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAFA8E70-BE96-4022-BFCA-B74467D1C631}">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ValidationTests.xlsx
+++ b/ValidationTests.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23426"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Mac\Home\OneDrive - DataSoar\Projects\Excel_Steps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB710A9-E12F-408B-A463-2C202774F28D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621628E9-AB98-4206-8454-664CA060C223}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1418" windowWidth="25312" windowHeight="15382" activeTab="2" xr2:uid="{9DD4A102-5F6B-46DA-8541-48C3A19AE79F}"/>
+    <workbookView xWindow="-22943" yWindow="2115" windowWidth="20161" windowHeight="12060" activeTab="3" xr2:uid="{9DD4A102-5F6B-46DA-8541-48C3A19AE79F}"/>
   </bookViews>
   <sheets>
     <sheet name="Lists" sheetId="2" r:id="rId1"/>
     <sheet name="Instructions" sheetId="583" r:id="rId2"/>
     <sheet name="Data" sheetId="587" r:id="rId3"/>
-    <sheet name="Original Data" sheetId="585" r:id="rId4"/>
-    <sheet name="ExcelSteps" sheetId="4" r:id="rId5"/>
+    <sheet name="Original Data" sheetId="646" r:id="rId4"/>
+    <sheet name="ExcelSteps" sheetId="647" r:id="rId5"/>
     <sheet name="XLStepsSettings" sheetId="588" state="veryHidden" r:id="rId6"/>
   </sheets>
   <definedNames>
@@ -41,7 +41,136 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="83">
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>Desc2</t>
+  </si>
+  <si>
+    <t>Desc3</t>
+  </si>
+  <si>
+    <t>Data_1</t>
+  </si>
+  <si>
+    <t>Data_2</t>
+  </si>
+  <si>
+    <t>Data_3</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>AA</t>
+  </si>
+  <si>
+    <t>BB</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>DD</t>
+  </si>
+  <si>
+    <t>BBB</t>
+  </si>
+  <si>
+    <t>EEE</t>
+  </si>
+  <si>
+    <t>FFF</t>
+  </si>
+  <si>
+    <t>GGG</t>
+  </si>
+  <si>
+    <t>HHH</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>List_Desc3</t>
+  </si>
+  <si>
+    <t>Calc_4</t>
+  </si>
+  <si>
+    <t>Calc_5</t>
+  </si>
+  <si>
+    <t>Calc_6</t>
+  </si>
+  <si>
+    <t>EE</t>
+  </si>
+  <si>
+    <t>This workbook contains validation cases for XLSteps</t>
+  </si>
+  <si>
+    <t>Part A</t>
+  </si>
+  <si>
+    <t>Refresh with dialog options as shown</t>
+  </si>
+  <si>
+    <t>Rows 2 - 11 of Excel Steps should result in a transformed table as shown</t>
+  </si>
+  <si>
+    <t>Populate worksheet, Data, with a copy of the table on Original Data</t>
+  </si>
+  <si>
+    <t>Carefully check all aspects of the Data_t table including presence of the column outline, width of Calc_6 and comment text</t>
+  </si>
+  <si>
+    <t>Part B</t>
+  </si>
+  <si>
+    <t>All Row 13-26 validation cases should produce a Refresh Error dialog box as shown and should label the Column C cell with a comment as shown</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>txtval</t>
+  </si>
+  <si>
+    <t>boolean1</t>
+  </si>
+  <si>
+    <t>boolean2</t>
+  </si>
+  <si>
+    <t>ShtNameFrm</t>
+  </si>
+  <si>
+    <t>Instructions</t>
+  </si>
+  <si>
+    <t>Original Data</t>
+  </si>
+  <si>
+    <t>cBoxAppShtName</t>
+  </si>
+  <si>
+    <t>Individually enable rows 13-27 as shown by entering "Data" in Columm A and refreshing the table again</t>
+  </si>
   <si>
     <t>Sheet</t>
   </si>
@@ -52,247 +181,115 @@
     <t>Step</t>
   </si>
   <si>
+    <t>Formula/List Name/Sort-by</t>
+  </si>
+  <si>
     <t>After or End Column</t>
   </si>
   <si>
     <t>Keep Formulas</t>
   </si>
   <si>
-    <t>Formula/List Name/Sort-by</t>
+    <t>Comment</t>
   </si>
   <si>
     <t>Number Format</t>
   </si>
   <si>
-    <t>Comment</t>
+    <t>Width</t>
+  </si>
+  <si>
+    <t>Col_Format</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Format with comment and width</t>
+  </si>
+  <si>
+    <t>Format with just comment</t>
+  </si>
+  <si>
+    <t>Col_Dropdown</t>
   </si>
   <si>
     <t>Col_Insert</t>
   </si>
   <si>
-    <t>Width</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Col_Dropdown</t>
+    <t>=@Data_Data_1*@Data_Data_2</t>
+  </si>
+  <si>
+    <t>Test insert with comment, number format and width</t>
+  </si>
+  <si>
+    <t>$#,##0.0000</t>
   </si>
   <si>
     <t>Col_AddGroup</t>
   </si>
   <si>
-    <t>$#,##0.0000</t>
-  </si>
-  <si>
-    <t>Col_Format</t>
+    <t>Tbl_Sort</t>
+  </si>
+  <si>
+    <t>Col_CondFormat</t>
+  </si>
+  <si>
+    <t>Descy</t>
+  </si>
+  <si>
+    <t>column not found error</t>
+  </si>
+  <si>
+    <t>column not specified</t>
+  </si>
+  <si>
+    <t>Dropdown range not specified</t>
+  </si>
+  <si>
+    <t>List_DescErr</t>
+  </si>
+  <si>
+    <t>Dropdown Range specified but not found</t>
+  </si>
+  <si>
+    <t>Column width is text not number</t>
   </si>
   <si>
     <t>a</t>
   </si>
   <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Desc</t>
-  </si>
-  <si>
-    <t>Desc2</t>
-  </si>
-  <si>
-    <t>Desc3</t>
-  </si>
-  <si>
-    <t>Data_1</t>
-  </si>
-  <si>
-    <t>Data_2</t>
-  </si>
-  <si>
-    <t>Data_3</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>AA</t>
-  </si>
-  <si>
-    <t>BB</t>
-  </si>
-  <si>
-    <t>CC</t>
-  </si>
-  <si>
-    <t>DD</t>
-  </si>
-  <si>
-    <t>BBB</t>
-  </si>
-  <si>
-    <t>EEE</t>
-  </si>
-  <si>
-    <t>FFF</t>
-  </si>
-  <si>
-    <t>GGG</t>
-  </si>
-  <si>
-    <t>Format with comment and width</t>
-  </si>
-  <si>
-    <t>Format with just comment</t>
-  </si>
-  <si>
-    <t>HHH</t>
-  </si>
-  <si>
-    <t>III</t>
-  </si>
-  <si>
-    <t>List_Desc3</t>
-  </si>
-  <si>
-    <t>Descy</t>
-  </si>
-  <si>
-    <t>List_DescErr</t>
-  </si>
-  <si>
-    <t>Calc_4</t>
-  </si>
-  <si>
-    <t>Calc_5</t>
-  </si>
-  <si>
-    <t>Calc_6</t>
-  </si>
-  <si>
-    <t>Test insert with comment, number format and width</t>
-  </si>
-  <si>
-    <t>EE</t>
-  </si>
-  <si>
-    <t>Tbl_Sort</t>
-  </si>
-  <si>
-    <t>Col_CondFormat</t>
-  </si>
-  <si>
     <t>Group start column not specified</t>
   </si>
   <si>
+    <t>Group end column not specified</t>
+  </si>
+  <si>
     <t>Group end column precedes start column</t>
   </si>
   <si>
     <t>Start and end columns are same</t>
   </si>
   <si>
-    <t>Column width is text not number</t>
-  </si>
-  <si>
-    <t>column not found error</t>
-  </si>
-  <si>
     <t>sort-by not specified</t>
   </si>
   <si>
-    <t>Dropdown Range specified but not found</t>
-  </si>
-  <si>
-    <t>Dropdown range not specified</t>
+    <t>Data_8</t>
   </si>
   <si>
     <t>Sort-by includes column not found</t>
   </si>
   <si>
-    <t>Data_8</t>
-  </si>
-  <si>
-    <t>column not specified</t>
-  </si>
-  <si>
     <t>Calc_8</t>
   </si>
   <si>
-    <t>This workbook contains validation cases for XLSteps</t>
-  </si>
-  <si>
-    <t>Part A</t>
-  </si>
-  <si>
-    <t>Refresh with dialog options as shown</t>
-  </si>
-  <si>
-    <t>Rows 2 - 11 of Excel Steps should result in a transformed table as shown</t>
-  </si>
-  <si>
-    <t>Populate worksheet, Data, with a copy of the table on Original Data</t>
-  </si>
-  <si>
-    <t>Carefully check all aspects of the Data_t table including presence of the column outline, width of Calc_6 and comment text</t>
-  </si>
-  <si>
-    <t>Group end column not specified</t>
-  </si>
-  <si>
-    <t>Part B</t>
+    <t>=(@Data_Data_1*@Data_Data_2))</t>
   </si>
   <si>
     <t>Excel formula error</t>
   </si>
   <si>
-    <t>All Row 13-26 validation cases should produce a Refresh Error dialog box as shown and should label the Column C cell with a comment as shown</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>txtval</t>
-  </si>
-  <si>
-    <t>boolean1</t>
-  </si>
-  <si>
-    <t>boolean2</t>
-  </si>
-  <si>
-    <t>ShtNameFrm</t>
-  </si>
-  <si>
-    <t>Instructions</t>
-  </si>
-  <si>
-    <t>Original Data</t>
-  </si>
-  <si>
-    <t>cBoxAppShtName</t>
-  </si>
-  <si>
-    <t>Data_t</t>
-  </si>
-  <si>
-    <t>=@Data_Data_1*@Data_Data_2</t>
-  </si>
-  <si>
-    <t>=(@Data_Data_1*@Data_Data_2))</t>
-  </si>
-  <si>
     <t>Missing Step name</t>
-  </si>
-  <si>
-    <t>Individually enable rows 13-27 as shown by entering "Data" in Columm A and refreshing the table again</t>
   </si>
 </sst>
 </file>
@@ -315,13 +312,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -331,6 +321,13 @@
     <font>
       <sz val="9"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -345,12 +342,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5"/>
       </patternFill>
     </fill>
   </fills>
@@ -395,45 +392,38 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="2" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Accent2" xfId="1" builtinId="33"/>
+    <cellStyle name="Accent2" xfId="2" builtinId="33"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="2" builtinId="10"/>
+    <cellStyle name="Note" xfId="1" builtinId="10"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1061,23 +1051,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
-        <v>39</v>
+      <c r="A1" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1093,43 +1083,43 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C3" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="3:3" x14ac:dyDescent="0.45">
       <c r="C32" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.45">
       <c r="C33" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="C47" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.45">
       <c r="C48" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1155,93 +1145,93 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D2">
-        <v>1.05</v>
+        <v>1.43</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>12.6</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D3">
-        <v>1.43</v>
+        <v>0.27</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F3">
-        <v>14.7</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D4">
-        <v>0.27</v>
+        <v>1.05</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>15.2</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D5">
         <v>0.1</v>
@@ -1255,13 +1245,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>5.0000000000000001E-3</v>
@@ -1274,7 +1264,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C6" xr:uid="{7CF90BFD-9717-4BCD-808D-A0D57D83FAE8}">
       <formula1>List_Desc3</formula1>
     </dataValidation>
@@ -1284,49 +1274,48 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D8AFF9-CA1C-4BB5-A9AF-B7045470B64B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE7BBC95-A30B-4711-9A8B-71C3AB1D2269}">
   <sheetPr codeName="Sheet5">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.59765625" customWidth="1"/>
     <col min="2" max="2" width="7.3984375" customWidth="1"/>
     <col min="3" max="3" width="12.59765625" customWidth="1"/>
     <col min="4" max="5" width="8.3984375" customWidth="1"/>
-    <col min="10" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>1.05</v>
@@ -1340,13 +1329,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>1.43</v>
@@ -1360,13 +1349,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D4">
         <v>0.27</v>
@@ -1380,13 +1369,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D5">
         <v>0.1</v>
@@ -1400,13 +1389,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>5.0000000000000001E-3</v>
@@ -1420,7 +1409,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C6" xr:uid="{CD76BD24-2C1A-432D-9076-1356F92F9B3E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C6" xr:uid="{D5312447-2219-41C9-9412-352F5F1CBCE5}">
       <formula1>List_Desc3</formula1>
     </dataValidation>
   </dataValidations>
@@ -1429,655 +1418,616 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39E15009-6303-4085-8153-5D82A08D8EC0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DE0505-8A1C-4A82-A36B-E9209DA69611}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.73046875" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.3984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.796875" style="14" customWidth="1"/>
-    <col min="5" max="5" width="10.06640625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="14.265625" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.9296875" style="15" customWidth="1"/>
-    <col min="8" max="8" width="15.1328125" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.3984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.73046875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.796875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="10.06640625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="14.265625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.9296875" style="10" customWidth="1"/>
+    <col min="8" max="8" width="15.1328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.3984375" style="8" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" x14ac:dyDescent="0.45">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5">
+        <v>12</v>
+      </c>
+      <c r="J2" s="8"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="11" t="s">
+      <c r="C3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="11" t="s">
+      <c r="C4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5">
+        <v>12</v>
+      </c>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2">
+      <c r="F6" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" ht="24" x14ac:dyDescent="0.45">
+      <c r="A8" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="5">
+        <v>15</v>
+      </c>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A11" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5">
         <v>12</v>
       </c>
-      <c r="J2" s="8"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="8"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5">
         <v>12</v>
       </c>
-      <c r="J4" s="8"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="8"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="4" t="s">
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J17" s="8"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="5"/>
+      <c r="G18" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="8"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="8"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="8"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="7"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="8"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="8"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="7"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="8"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="2" t="b">
+      <c r="E26" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" ht="24" x14ac:dyDescent="0.45">
-      <c r="A8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="2" t="b">
+      <c r="G26" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="2">
-        <v>15</v>
-      </c>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="8"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="6" t="s">
+      <c r="C27" s="5"/>
+      <c r="D27" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="8"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="8"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="8"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="8"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="8"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="8"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="8"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="8"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="6" t="s">
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C30" xr:uid="{D80040AE-46D1-4EE6-8B5B-564647569365}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C27" xr:uid="{C804319C-00CD-477C-8F39-E2668FA432AF}">
       <formula1>"Col_Format,Col_Insert,Col_AddGroup,Col_CondFormat,Col_Dropdown,Tbl_FreezeRow1,Tbl_Sort"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAFA8E70-BE96-4022-BFCA-B74467D1C631}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="C2" t="b">
         <v>0</v>
@@ -2088,10 +2038,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
@@ -2102,10 +2052,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="C4" t="b">
         <v>0</v>
@@ -2116,7 +2066,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C5" t="b">
         <v>0</v>
@@ -2127,24 +2077,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" t="b">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/ValidationTests.xlsx
+++ b/ValidationTests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Mac\Home\OneDrive - DataSoar\Projects\Excel_Steps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621628E9-AB98-4206-8454-664CA060C223}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C06E1FD-9D77-45FD-8FE3-BB0F11529AD1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22943" yWindow="2115" windowWidth="20161" windowHeight="12060" activeTab="3" xr2:uid="{9DD4A102-5F6B-46DA-8541-48C3A19AE79F}"/>
+    <workbookView xWindow="4133" yWindow="4035" windowWidth="20159" windowHeight="12060" activeTab="2" xr2:uid="{9DD4A102-5F6B-46DA-8541-48C3A19AE79F}"/>
   </bookViews>
   <sheets>
     <sheet name="Lists" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="84">
   <si>
     <t>Data</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>Missing Step name</t>
+  </si>
+  <si>
+    <t>Data_t</t>
   </si>
 </sst>
 </file>
@@ -395,7 +398,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1"/>
@@ -419,6 +422,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent2" xfId="2" builtinId="33"/>
@@ -1562,11 +1566,11 @@
       <c r="C6" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="11" t="s">
         <v>58</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6" s="5" t="b">
         <v>1</v>
@@ -2005,7 +2009,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAFA8E70-BE96-4022-BFCA-B74467D1C631}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
@@ -2083,6 +2087,20 @@
         <v>1</v>
       </c>
     </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
